--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484145_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484145_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1463</v>
+        <v>7.6108</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2668</v>
+        <v>7.3485</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.2623</v>
       </c>
       <c r="G2" t="n">
         <v>5.6306</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3569</v>
+        <v>-0.1786</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5476</v>
+        <v>0.6293</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1907</v>
+        <v>-0.8079</v>
       </c>
       <c r="V2" t="n">
         <v>2.754</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3308</v>
+        <v>6.4736</v>
       </c>
       <c r="E3" t="n">
-        <v>9.138</v>
+        <v>8.831899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8072</v>
+        <v>-2.3583</v>
       </c>
       <c r="G3" t="n">
         <v>5.4484</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9193</v>
+        <v>-0.7765</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6803</v>
+        <v>0.3743</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.5997</v>
+        <v>-1.1508</v>
       </c>
       <c r="V3" t="n">
         <v>1.405</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.049</v>
+        <v>1.3754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9597</v>
+        <v>1.0617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0893</v>
+        <v>0.3138</v>
       </c>
       <c r="G4" t="n">
         <v>1.9776</v>
@@ -766,13 +766,13 @@
         <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4601</v>
+        <v>-1.1337</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2108</v>
+        <v>-0.9863</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0636</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7275</v>
+        <v>0.6153</v>
       </c>
       <c r="E5" t="n">
         <v>-0.0422</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.6575</v>
       </c>
       <c r="G5" t="n">
         <v>0.2922</v>
@@ -844,13 +844,13 @@
         <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0385</v>
+        <v>-0.0737</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1009</v>
+        <v>-0.0113</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9361</v>
+        <v>-0.7499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6835</v>
+        <v>0.7855</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6195</v>
+        <v>-1.5354</v>
       </c>
       <c r="G6" t="n">
         <v>0.8228</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2783</v>
+        <v>-0.0921</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.216</v>
+        <v>-0.1318</v>
       </c>
       <c r="V6" t="n">
         <v>-2.0757</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4988</v>
+        <v>-1.1652</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2618</v>
+        <v>-0.1642</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2371</v>
+        <v>-1.001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7791</v>
+        <v>-0.7462</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-1.0533</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0789</v>
+        <v>0.3071</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0556</v>
+        <v>-0.1408</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1051</v>
+        <v>-0.9466</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1606</v>
+        <v>0.8058</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8347</v>
+        <v>-0.6054</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5951</v>
+        <v>-0.1067</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2396</v>
+        <v>-0.4986</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6099</v>
+        <v>-0.931</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6746</v>
+        <v>0.1191</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.0502</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9328</v>
+        <v>-0.6783</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.1425</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9328</v>
+        <v>-0.5358000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8428</v>
+        <v>-1.6005</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7295</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1133</v>
+        <v>-0.973</v>
       </c>
       <c r="G8" t="n">
         <v>-2.824</v>
@@ -1078,13 +1078,13 @@
         <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8247</v>
+        <v>-0.5824</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1248</v>
+        <v>0.2269</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9495</v>
+        <v>-0.8093</v>
       </c>
       <c r="V8" t="n">
         <v>1.8059</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0128</v>
+        <v>-1.7067</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4694</v>
+        <v>1.7755</v>
       </c>
       <c r="F9" t="n">
         <v>-3.4822</v>
@@ -1156,10 +1156,10 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9523</v>
+        <v>-0.6462</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1813</v>
+        <v>0.1248</v>
       </c>
       <c r="U9" t="n">
         <v>-0.771</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0554</v>
+        <v>-2.3354</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0825</v>
+        <v>-0.8739</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.973</v>
+        <v>-1.4615</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7462</v>
+        <v>-0.7791</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0533</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3071</v>
+        <v>-0.0789</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1408</v>
+        <v>0.0556</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9466</v>
+        <v>-0.1051</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8058</v>
+        <v>0.1606</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6054</v>
+        <v>-0.8347</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1067</v>
+        <v>-0.5951</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4986</v>
+        <v>-0.2396</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1903</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8213</v>
+        <v>-0.2268</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7991</v>
+        <v>0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0221</v>
+        <v>-0.2892</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6783</v>
+        <v>-0.9328</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1425</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.9328</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2355</v>
+        <v>-3.8453</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1378</v>
+        <v>-2.8317</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0977</v>
+        <v>-1.0135</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4425</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9358</v>
+        <v>-0.5456</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3174</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3124</v>
+        <v>-0.2282</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6669</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.672199999999998</v>
+        <v>4.672099999999999</v>
       </c>
       <c r="E12" t="n">
         <v>15.2636</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.5915</v>
+        <v>-10.5913</v>
       </c>
       <c r="G12" t="n">
         <v>10.8507</v>
@@ -1363,7 +1363,7 @@
         <v>11.5308</v>
       </c>
       <c r="J12" t="n">
-        <v>17.1077</v>
+        <v>17.10769999999999</v>
       </c>
       <c r="K12" t="n">
         <v>3.1811</v>
@@ -1375,7 +1375,7 @@
         <v>-6.2571</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.861299999999999</v>
+        <v>-3.8613</v>
       </c>
       <c r="O12" t="n">
         <v>-2.3957</v>
@@ -1390,16 +1390,16 @@
         <v>9.9193</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.186500000000001</v>
+        <v>-5.186600000000001</v>
       </c>
       <c r="T12" t="n">
         <v>1.0494</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.236000000000001</v>
+        <v>-6.236</v>
       </c>
       <c r="V12" t="n">
-        <v>9.999999999987796e-05</v>
+        <v>9.999999999965592e-05</v>
       </c>
       <c r="W12" t="n">
         <v>8.0176</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.6715</v>
+        <v>8.284800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>10.8104</v>
+        <v>9.484</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1389</v>
+        <v>-1.1992</v>
       </c>
       <c r="G13" t="n">
         <v>0.7441</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8392</v>
+        <v>1.4525</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8683</v>
+        <v>1.5419</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0291</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>5.8898</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7555</v>
+        <v>2.625</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9357</v>
+        <v>2.3274</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8198</v>
+        <v>0.2977</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.104</v>
+        <v>1.5023</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6048</v>
+        <v>2.0866</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7088</v>
+        <v>-0.5843</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1388</v>
+        <v>2.5483</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6558</v>
+        <v>1.9408</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.517</v>
+        <v>0.6075</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2428</v>
+        <v>-1.046</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0509</v>
+        <v>0.1458</v>
       </c>
       <c r="O14" t="n">
         <v>-1.1918</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7882</v>
+        <v>0.9126</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7889</v>
+        <v>0.7709</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.1416</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6745</v>
+        <v>0.4085</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6745</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5667</v>
+        <v>2.3882</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4234</v>
+        <v>2.5254</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1433</v>
+        <v>-0.1372</v>
       </c>
       <c r="G15" t="n">
         <v>1.6825</v>
@@ -1624,13 +1624,13 @@
         <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>0.289</v>
+        <v>0.1105</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.051</v>
+        <v>0.051</v>
       </c>
       <c r="U15" t="n">
-        <v>0.34</v>
+        <v>0.0595</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5363</v>
+        <v>1.4113</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6643</v>
+        <v>0.5073</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1279</v>
+        <v>0.904</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2763</v>
+        <v>-1.104</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8016</v>
+        <v>0.6048</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0779</v>
+        <v>-1.7088</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9779</v>
+        <v>0.1388</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.6558</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1205</v>
+        <v>-0.517</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2542</v>
+        <v>-1.2428</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0558</v>
+        <v>-0.0509</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1983</v>
+        <v>-1.1918</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7531</v>
+        <v>1.444</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4204</v>
+        <v>1.3605</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3327</v>
+        <v>0.0835</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9405</v>
+        <v>0.6745</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2783</v>
+        <v>0.4595</v>
       </c>
       <c r="E17" t="n">
-        <v>1.205</v>
+        <v>1.1576</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0732</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5023</v>
+        <v>-0.6468</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0866</v>
+        <v>0.6851</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5843</v>
+        <v>-1.3318</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5483</v>
+        <v>1.0106</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9408</v>
+        <v>1.0081</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6075</v>
+        <v>0.0026</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.046</v>
+        <v>-1.6574</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1458</v>
+        <v>-0.323</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1918</v>
+        <v>-1.3344</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4342</v>
+        <v>-0.4293</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3514</v>
+        <v>-0.119</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0828</v>
+        <v>-0.3104</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4085</v>
+        <v>0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4085</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1229</v>
+        <v>0.0798</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8515</v>
+        <v>2.2358</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9744</v>
+        <v>-2.156</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6468</v>
+        <v>-0.2763</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6851</v>
+        <v>0.8016</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3318</v>
+        <v>-1.0779</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0106</v>
+        <v>0.9779</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0081</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0026</v>
+        <v>0.1205</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6574</v>
+        <v>-1.2542</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.323</v>
+        <v>-0.0558</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3344</v>
+        <v>-1.1983</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0117</v>
+        <v>1.2966</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4251</v>
+        <v>0.992</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5867</v>
+        <v>0.3046</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9405</v>
+        <v>-0.9405</v>
       </c>
       <c r="W18" t="n">
         <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6745</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2024</v>
+        <v>-1.2705</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4104</v>
+        <v>-0.3901</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.792</v>
+        <v>-0.8804</v>
       </c>
       <c r="G19" t="n">
         <v>-4.1779</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2347</v>
+        <v>0.6972</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2833</v>
+        <v>0.737</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0486</v>
+        <v>-0.0398</v>
       </c>
       <c r="V19" t="n">
         <v>1.615</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0367</v>
+        <v>-2.7095</v>
       </c>
       <c r="E20" t="n">
-        <v>0.343</v>
+        <v>0.0211</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3797</v>
+        <v>-2.7307</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1675</v>
+        <v>-2.5805</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5087</v>
+        <v>-0.1965</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6762</v>
+        <v>-2.3839</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0882</v>
+        <v>-1.0017</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9678</v>
+        <v>-0.2112</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1205</v>
+        <v>-0.7905</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2558</v>
+        <v>-1.5788</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.459</v>
+        <v>0.0147</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7967</v>
+        <v>-1.5935</v>
       </c>
       <c r="P20" t="n">
         <v>0.7935</v>
@@ -2014,28 +2014,28 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.238</v>
+        <v>0.5498</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2665</v>
+        <v>0.4195</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5044999999999999</v>
+        <v>0.1303</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.4247</v>
+        <v>-1.4724</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.0118</v>
+        <v>0.6032</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4129</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.842</v>
+        <v>-3.1047</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9992</v>
+        <v>0.1389</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8429</v>
+        <v>-3.2436</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5805</v>
+        <v>-0.1675</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1965</v>
+        <v>0.5087</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3839</v>
+        <v>-0.6762</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0017</v>
+        <v>1.0882</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2112</v>
+        <v>0.9678</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7905</v>
+        <v>0.1205</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5788</v>
+        <v>-1.2558</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0147</v>
+        <v>-0.459</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5935</v>
+        <v>-0.7967</v>
       </c>
       <c r="P21" t="n">
         <v>0.7935</v>
@@ -2092,22 +2092,22 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5827</v>
+        <v>-0.3061</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6008</v>
+        <v>0.0624</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0181</v>
+        <v>-0.3685</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4724</v>
+        <v>-3.4247</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6032</v>
+        <v>-1.0118</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0757</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2347</v>
+        <v>-3.9048</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2819</v>
+        <v>-1.9758</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9528</v>
+        <v>-1.929</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1004</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2732</v>
+        <v>0.0567</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0452</v>
+        <v>0.2608</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2279</v>
+        <v>-0.2041</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.041700000000001</v>
+        <v>-8.250999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9503</v>
+        <v>-5.4402</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0914</v>
+        <v>-2.8108</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7263</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7085</v>
+        <v>0.0822</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3514</v>
+        <v>0.1588</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3571</v>
+        <v>-0.0766</v>
       </c>
       <c r="V23" t="n">
         <v>-3.4247</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6721</v>
+        <v>-3.991899999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>10.5915</v>
+        <v>10.5914</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.2637</v>
+        <v>-14.5833</v>
       </c>
       <c r="G24" t="n">
         <v>-10.8508</v>
@@ -2299,7 +2299,7 @@
         <v>-11.5306</v>
       </c>
       <c r="J24" t="n">
-        <v>6.256899999999998</v>
+        <v>6.2569</v>
       </c>
       <c r="K24" t="n">
         <v>3.8615</v>
@@ -2326,19 +2326,19 @@
         <v>10.9111</v>
       </c>
       <c r="S24" t="n">
-        <v>5.1865</v>
+        <v>5.866700000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>6.235899999999998</v>
+        <v>6.2358</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0493</v>
+        <v>-0.3693</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>8.0177</v>
+        <v>8.017700000000001</v>
       </c>
       <c r="X24" t="n">
         <v>-8.017799999999999</v>
